--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -278,22 +278,58 @@
     </r>
   </si>
   <si>
-    <t>物流时效（海运）</t>
-  </si>
-  <si>
-    <t>发货频率（海运)</t>
-  </si>
-  <si>
-    <t>优先级（海运)</t>
-  </si>
-  <si>
-    <t>物流时效（***）</t>
-  </si>
-  <si>
-    <t>发货频率（***）</t>
-  </si>
-  <si>
-    <t>优先级（***）</t>
+    <t>物流时效（空运）</t>
+  </si>
+  <si>
+    <t>发货频率（空运)</t>
+  </si>
+  <si>
+    <t>优先级（空运)</t>
+  </si>
+  <si>
+    <t>物流时效（快递）</t>
+  </si>
+  <si>
+    <t>发货频率（快递）</t>
+  </si>
+  <si>
+    <t>优先级（快递）</t>
+  </si>
+  <si>
+    <t>物流时效（海运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（海运散装）</t>
+  </si>
+  <si>
+    <t>优先级（海运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（海运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（海运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（海运整柜)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运散装）</t>
+  </si>
+  <si>
+    <t>优先级（铁运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（铁运整柜)</t>
   </si>
   <si>
     <t>序号</t>
@@ -1573,7 +1609,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="4" max="4" width="13.125" customWidth="1"/>
@@ -1588,11 +1624,13 @@
     <col min="13" max="13" width="12.75" customWidth="1"/>
     <col min="14" max="14" width="11.375" customWidth="1"/>
     <col min="15" max="15" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="16" max="16" width="17.875" customWidth="1"/>
+    <col min="17" max="25" width="17.375" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:18">
+    <row r="1" ht="15" customHeight="1" spans="1:28">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1619,14 +1657,24 @@
       <c r="N1" s="10"/>
       <c r="O1" s="10"/>
       <c r="P1" s="10"/>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:28">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1664,13 +1712,43 @@
         <v>17</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1679,8 +1757,8 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1713,19 +1791,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1764,13 +1842,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1786,38 +1864,38 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" ht="14.25" spans="1:19">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1868,19 +1946,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -1896,7 +1974,7 @@
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" ht="14.25" spans="1:21">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1905,31 +1983,31 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1965,7 +2043,7 @@
     <col min="8" max="8" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" ht="14.25" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1976,19 +2054,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
@@ -2035,28 +2113,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -332,148 +332,148 @@
     <t>优先级（铁运整柜)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规则名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFF54A45"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开始日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFF54A45"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结束日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>备货系数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>默认日销量类型</t>
+    </r>
+  </si>
+  <si>
+    <t>固定日销量</t>
+  </si>
+  <si>
+    <t>动态日销量</t>
+  </si>
+  <si>
+    <t>3天日均（%）</t>
+  </si>
+  <si>
+    <t>7天日均（%）</t>
+  </si>
+  <si>
+    <t>14天日均（%）</t>
+  </si>
+  <si>
+    <t>30天日均（%）</t>
+  </si>
+  <si>
+    <t>60天日均（%）</t>
+  </si>
+  <si>
+    <t>90天日均（%）</t>
+  </si>
+  <si>
+    <t>180天日均（%）</t>
+  </si>
+  <si>
+    <t>270天日均（%）</t>
+  </si>
+  <si>
+    <t>360天日均（%）</t>
+  </si>
+  <si>
     <t>序号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规则名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFF54A45"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>开始日期</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFF54A45"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>结束日期</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>备货系数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>默认日销量类型</t>
-    </r>
-  </si>
-  <si>
-    <t>固定日销量</t>
-  </si>
-  <si>
-    <t>动态日销量</t>
-  </si>
-  <si>
-    <t>3天日均（%）</t>
-  </si>
-  <si>
-    <t>7天日均（%）</t>
-  </si>
-  <si>
-    <t>14天日均（%）</t>
-  </si>
-  <si>
-    <t>30天日均（%）</t>
-  </si>
-  <si>
-    <t>60天日均（%）</t>
-  </si>
-  <si>
-    <t>90天日均（%）</t>
-  </si>
-  <si>
-    <t>180天日均（%）</t>
-  </si>
-  <si>
-    <t>270天日均（%）</t>
-  </si>
-  <si>
-    <t>360天日均（%）</t>
   </si>
   <si>
     <r>
@@ -1769,18 +1769,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="5" max="5" width="11.75" customWidth="1"/>
-    <col min="6" max="6" width="11.875" customWidth="1"/>
-    <col min="7" max="8" width="12.5" customWidth="1"/>
+    <col min="2" max="4" width="11.75" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="7" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,20 +1788,17 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1842,13 +1837,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1871,31 +1866,31 @@
       <c r="D2" s="2"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="N2" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1946,16 +1941,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>47</v>
@@ -1983,31 +1978,31 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -2054,16 +2049,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>48</v>
@@ -2116,16 +2111,16 @@
         <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>50</v>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -419,6 +419,68 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>默认日销量类型</t>
+    </r>
+  </si>
+  <si>
+    <t>固定日销量</t>
+  </si>
+  <si>
+    <t>动态日销量</t>
+  </si>
+  <si>
+    <t>3天日均（%）</t>
+  </si>
+  <si>
+    <t>7天日均（%）</t>
+  </si>
+  <si>
+    <t>14天日均（%）</t>
+  </si>
+  <si>
+    <t>30天日均（%）</t>
+  </si>
+  <si>
+    <t>60天日均（%）</t>
+  </si>
+  <si>
+    <t>90天日均（%）</t>
+  </si>
+  <si>
+    <t>180天日均（%）</t>
+  </si>
+  <si>
+    <t>270天日均（%）</t>
+  </si>
+  <si>
+    <t>360天日均（%）</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开始日期</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
@@ -436,44 +498,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>默认日销量类型</t>
-    </r>
-  </si>
-  <si>
-    <t>固定日销量</t>
-  </si>
-  <si>
-    <t>动态日销量</t>
-  </si>
-  <si>
-    <t>3天日均（%）</t>
-  </si>
-  <si>
-    <t>7天日均（%）</t>
-  </si>
-  <si>
-    <t>14天日均（%）</t>
-  </si>
-  <si>
-    <t>30天日均（%）</t>
-  </si>
-  <si>
-    <t>60天日均（%）</t>
-  </si>
-  <si>
-    <t>90天日均（%）</t>
-  </si>
-  <si>
-    <t>180天日均（%）</t>
-  </si>
-  <si>
-    <t>270天日均（%）</t>
-  </si>
-  <si>
-    <t>360天日均（%）</t>
-  </si>
-  <si>
-    <t>序号</t>
+      <t>动态日销量</t>
+    </r>
   </si>
   <si>
     <r>
@@ -494,18 +520,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>动态日销量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>固定日销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -516,29 +535,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>固定日销量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>店铺/渠道</t>
+      <t>店铺</t>
     </r>
   </si>
   <si>
@@ -578,14 +575,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFF54A45"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFF54A45"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1268,16 +1265,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1286,16 +1283,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1778,7 +1775,7 @@
     <col min="6" max="7" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1791,10 +1788,10 @@
       <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1860,10 +1857,10 @@
       <c r="S1" s="4"/>
     </row>
     <row r="2" ht="14.25" spans="1:19">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8" t="s">
         <v>37</v>
@@ -1916,21 +1913,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="10" width="13.75" customWidth="1"/>
-    <col min="11" max="11" width="14.125" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="14.5" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="9" width="13.75" customWidth="1"/>
+    <col min="10" max="10" width="14.125" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:21">
+    <row r="1" ht="15" customHeight="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1940,86 +1937,81 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
     </row>
-    <row r="2" ht="14.25" spans="1:21">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+    <row r="2" spans="1:20">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="H2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="H1:P1"/>
+  <mergeCells count="7">
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2029,16 +2021,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="12.125" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:21">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2048,21 +2040,19 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -2075,7 +2065,6 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2086,21 +2075,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
     <col min="3" max="3" width="13.875" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="15.125" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="14.25" spans="1:23">
+    <row r="1" customFormat="1" ht="14.25" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2110,27 +2098,25 @@
       <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="G1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -2143,7 +2129,6 @@
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <r>
       <rPr>
@@ -419,6 +419,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -467,16 +474,24 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>开始日期</t>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>动态日销量</t>
     </r>
   </si>
   <si>
@@ -498,18 +513,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>动态日销量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>固定日销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>*</t>
     </r>
     <r>
@@ -520,26 +528,8 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>固定日销量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>店铺</t>
-    </r>
-  </si>
-  <si>
-    <t>*去噪类型</t>
+      <t>去噪类型</t>
+    </r>
   </si>
   <si>
     <t>百分比去噪（%）</t>
@@ -1941,13 +1931,13 @@
         <v>30</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -1963,7 +1953,7 @@
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" ht="14.25" spans="1:20">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2030,7 +2020,7 @@
     <col min="7" max="7" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" ht="14.25" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2050,7 +2040,7 @@
         <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -2096,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>30</v>
@@ -2107,14 +2097,14 @@
       <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="备货" sheetId="1" r:id="rId1"/>
@@ -518,6 +518,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -125,157 +125,25 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFF54A45"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>安全天数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>默认备货系数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购审批（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生产周期（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>供应商发货（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>质检入库（天）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>采购频率（天）</t>
-    </r>
+    <t>安全天数</t>
+  </si>
+  <si>
+    <t>默认备货系数</t>
+  </si>
+  <si>
+    <t>采购审批（天）</t>
+  </si>
+  <si>
+    <t>生产周期（天）</t>
+  </si>
+  <si>
+    <t>供应商发货（天）</t>
+  </si>
+  <si>
+    <t>质检入库（天）</t>
+  </si>
+  <si>
+    <t>采购频率（天）</t>
   </si>
   <si>
     <t>物流时效（空运）</t>
@@ -592,6 +460,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -733,12 +607,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1119,137 +987,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1290,6 +1158,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1661,10 +1532,10 @@
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
       <c r="Z1" s="13"/>
-      <c r="AA1" s="13" t="s">
+      <c r="AA1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1672,19 +1543,19 @@
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="11" t="s">

--- a/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/replenishmentRuleTemplate.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="备货" sheetId="1" r:id="rId1"/>
+    <sheet name="时效 &amp; 备货" sheetId="1" r:id="rId1"/>
     <sheet name="动态备货系数" sheetId="2" r:id="rId2"/>
     <sheet name="默认日销量" sheetId="3" r:id="rId3"/>
     <sheet name="动态日销量" sheetId="4" r:id="rId4"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="52">
   <si>
     <r>
       <rPr>
@@ -125,79 +125,82 @@
     </r>
   </si>
   <si>
+    <t>备货</t>
+  </si>
+  <si>
+    <t>采购审批（天）</t>
+  </si>
+  <si>
+    <t>生产周期（天）</t>
+  </si>
+  <si>
+    <t>供应商发货（天）</t>
+  </si>
+  <si>
+    <t>质检入库（天）</t>
+  </si>
+  <si>
+    <t>采购频率（天）</t>
+  </si>
+  <si>
+    <t>物流时效（空运）</t>
+  </si>
+  <si>
+    <t>发货频率（空运)</t>
+  </si>
+  <si>
+    <t>优先级（空运)</t>
+  </si>
+  <si>
+    <t>物流时效（快递）</t>
+  </si>
+  <si>
+    <t>发货频率（快递）</t>
+  </si>
+  <si>
+    <t>优先级（快递）</t>
+  </si>
+  <si>
+    <t>物流时效（海运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（海运散装）</t>
+  </si>
+  <si>
+    <t>优先级（海运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（海运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（海运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（海运整柜)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运散装）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运散装）</t>
+  </si>
+  <si>
+    <t>优先级（铁运散装)</t>
+  </si>
+  <si>
+    <t>物流时效（铁运整柜）</t>
+  </si>
+  <si>
+    <t>发货频率（铁运整柜）</t>
+  </si>
+  <si>
+    <t>优先级（铁运整柜)</t>
+  </si>
+  <si>
     <t>安全天数</t>
   </si>
   <si>
     <t>默认备货系数</t>
-  </si>
-  <si>
-    <t>采购审批（天）</t>
-  </si>
-  <si>
-    <t>生产周期（天）</t>
-  </si>
-  <si>
-    <t>供应商发货（天）</t>
-  </si>
-  <si>
-    <t>质检入库（天）</t>
-  </si>
-  <si>
-    <t>采购频率（天）</t>
-  </si>
-  <si>
-    <t>物流时效（空运）</t>
-  </si>
-  <si>
-    <t>发货频率（空运)</t>
-  </si>
-  <si>
-    <t>优先级（空运)</t>
-  </si>
-  <si>
-    <t>物流时效（快递）</t>
-  </si>
-  <si>
-    <t>发货频率（快递）</t>
-  </si>
-  <si>
-    <t>优先级（快递）</t>
-  </si>
-  <si>
-    <t>物流时效（海运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（海运散装）</t>
-  </si>
-  <si>
-    <t>优先级（海运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（海运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（海运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（海运整柜)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运散装）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运散装）</t>
-  </si>
-  <si>
-    <t>优先级（铁运散装)</t>
-  </si>
-  <si>
-    <t>物流时效（铁运整柜）</t>
-  </si>
-  <si>
-    <t>发货频率（铁运整柜）</t>
-  </si>
-  <si>
-    <t>优先级（铁运整柜)</t>
   </si>
   <si>
     <r>
@@ -816,7 +819,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -858,6 +861,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -993,7 +1022,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1005,34 +1034,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1117,7 +1146,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1160,7 +1189,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1535,95 +1573,96 @@
       <c r="AA1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="AB1" s="15"/>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="P2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="Q2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="S2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="X2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="Y2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Z2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="AA2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="10"/>
+      <c r="AB2" s="17" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="I1:P1"/>
+    <mergeCell ref="AA1:AB1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1654,16 +1693,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1702,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1731,31 +1770,31 @@
       <c r="D2" s="3"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
@@ -1806,16 +1845,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -1839,31 +1878,31 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1909,16 +1948,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -1967,22 +2006,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
